--- a/results 4 workers/Results 4 workers.xlsx
+++ b/results 4 workers/Results 4 workers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumentumok_2026\PS\Revision\Logs Results revision\results 4 workers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumentumok_2026\PS\Revision\For resubmit\Repository\results 4 workers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E28000-318D-483E-BF64-7249250AE2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795409BF-D4C7-40DD-B832-28468046EEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1293,7 +1293,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4332,6 +4332,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="V55:W55"/>
+    <mergeCell ref="V57:W57"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="S62:T62"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V54:W54"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="F39:G39"/>
@@ -4342,15 +4351,6 @@
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F49:G49"/>
-    <mergeCell ref="V55:W55"/>
-    <mergeCell ref="V57:W57"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="S62:T62"/>
-    <mergeCell ref="V48:W48"/>
-    <mergeCell ref="V49:W49"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="V54:W54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
